--- a/single-api/criteo-api/swagger_modules.xlsx
+++ b/single-api/criteo-api/swagger_modules.xlsx
@@ -78,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,6 +92,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -518,6 +521,11 @@
           <t>接口覆盖率</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>模块路径</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -547,6 +555,11 @@
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\0-1CurrencyInfoController</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -580,6 +593,11 @@
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>0% (0/20)</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\1-Schedule</t>
         </is>
       </c>
     </row>
@@ -611,6 +629,11 @@
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="2" t="n"/>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\1-sharelink</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -640,6 +663,11 @@
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="n"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\提供给下载中心的查询接口</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -669,6 +697,11 @@
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="n"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\advertising-controller</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -698,6 +731,11 @@
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="2" t="n"/>
       <c r="I7" s="2" t="n"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\advertising模块异步下载接口</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -727,6 +765,11 @@
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\balance-controller</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -756,6 +799,11 @@
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="n"/>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\bid-multiplier-controller</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -785,6 +833,11 @@
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
       <c r="I10" s="2" t="n"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\budget-line-item-controller</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -814,6 +867,11 @@
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="n"/>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\campaigns-controller</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -847,6 +905,11 @@
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0% (0/17)</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\category-controller</t>
         </is>
       </c>
     </row>
@@ -878,6 +941,11 @@
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="n"/>
       <c r="I13" s="2" t="n"/>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\custom-dashboard-controller</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -911,6 +979,11 @@
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0% (0/9)</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\dashboard-controller</t>
         </is>
       </c>
     </row>
@@ -942,6 +1015,11 @@
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="n"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\dashboard-new-controller</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -975,6 +1053,11 @@
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0% (0/17)</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\day-parting-controller</t>
         </is>
       </c>
     </row>
@@ -1006,6 +1089,11 @@
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\Default Report异步下载接口</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1035,6 +1123,11 @@
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
       <c r="I18" s="2" t="n"/>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\default-report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1064,6 +1157,11 @@
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="n"/>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\event-controller</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1097,6 +1195,11 @@
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\health-controller</t>
         </is>
       </c>
     </row>
@@ -1128,6 +1231,11 @@
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\Home页相关异步下载接口</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1157,6 +1265,11 @@
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
       <c r="I22" s="2" t="n"/>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\Keyword相关接口</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1186,6 +1299,11 @@
       <c r="G23" s="2" t="n"/>
       <c r="H23" s="2" t="n"/>
       <c r="I23" s="2" t="n"/>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\line-items-controller</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1221,6 +1339,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\manual-edit-data-base-controller</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1254,6 +1377,11 @@
       <c r="I25" s="2" t="inlineStr">
         <is>
           <t>0% (0/25)</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\my-report-controller</t>
         </is>
       </c>
     </row>
@@ -1285,6 +1413,11 @@
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
       <c r="I26" s="2" t="n"/>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\NegativeKeyword相关接口</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1314,6 +1447,11 @@
       <c r="G27" s="2" t="n"/>
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="n"/>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\notification-controller</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1343,6 +1481,11 @@
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\operation-log-controller</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1376,6 +1519,11 @@
       <c r="I29" s="2" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\profile-currency-controller</t>
         </is>
       </c>
     </row>
@@ -1407,6 +1555,11 @@
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
       <c r="I30" s="2" t="n"/>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1440,6 +1593,11 @@
       <c r="I31" s="2" t="inlineStr">
         <is>
           <t>0% (0/16)</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\report-export-controller</t>
         </is>
       </c>
     </row>
@@ -1471,6 +1629,11 @@
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="n"/>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\rule-apply-controller</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1500,6 +1663,11 @@
       <c r="G33" s="2" t="n"/>
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="n"/>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\rule-apply-v-2-controller</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1529,6 +1697,11 @@
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
       <c r="I34" s="2" t="n"/>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\rule-controller</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1562,6 +1735,11 @@
       <c r="I35" s="2" t="inlineStr">
         <is>
           <t>0% (0/10)</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\Sov Share Link</t>
         </is>
       </c>
     </row>
@@ -1593,6 +1771,11 @@
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="n"/>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\sov-controller</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1622,6 +1805,11 @@
       <c r="G37" s="2" t="n"/>
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="n"/>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\sov-report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1657,6 +1845,11 @@
           <t>0% (0/1)</t>
         </is>
       </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\sync-task-controller</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1690,6 +1883,11 @@
       <c r="I39" s="2" t="inlineStr">
         <is>
           <t>0% (0/2)</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\system-check-controller</t>
         </is>
       </c>
     </row>
@@ -1721,6 +1919,11 @@
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
       <c r="I40" s="2" t="n"/>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\tag-report-controller</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1750,6 +1953,11 @@
       <c r="G41" s="2" t="n"/>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\tag-rule-controller</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1779,6 +1987,11 @@
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\Top Bar-同步数据相关接口</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1812,6 +2025,11 @@
       <c r="I43" s="2" t="inlineStr">
         <is>
           <t>0% (0/1)</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\unbind-or-unmange-controller</t>
         </is>
       </c>
     </row>
@@ -1843,6 +2061,11 @@
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\user-controller</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1872,6 +2095,11 @@
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="n"/>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>ai_api\single-api\criteo-api\us\CriteoApi\user-location-controller</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
